--- a/GL ADV 03-2026 14052026.XLSX
+++ b/GL ADV 03-2026 14052026.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Dashboard JPKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A6FB49-F7A8-4505-8277-46D0F09923F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EC6CF7-FB6F-42AB-96FB-A51F21C91B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ALL!$A$1:$AI$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DATA!$A$1:$E$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">DATA!$A$1:$G$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3230" uniqueCount="521">
   <si>
     <t/>
   </si>
@@ -1548,9 +1548,6 @@
     <t>NAMA</t>
   </si>
   <si>
-    <t xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</t>
-  </si>
-  <si>
     <t>A72202</t>
   </si>
   <si>
@@ -1567,6 +1564,45 @@
   </si>
   <si>
     <t>BYR BALIK</t>
+  </si>
+  <si>
+    <t>PTJ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABMJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABMSbh</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABMSel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABMSrwk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIDB IBS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIDB Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIDBeC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIDBH</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CIDB Digital Sdn Bhd</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ABMU</t>
+  </si>
+  <si>
+    <t>NAMA1</t>
   </si>
 </sst>
 </file>
@@ -1680,7 +1716,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1765,6 +1801,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13409,17 +13457,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357F5962-F6D2-46FD-BFC8-B16168739F3B}">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1796875" customWidth="1"/>
     <col min="2" max="2" width="30.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
-    <col min="4" max="4" width="16.453125" customWidth="1"/>
-    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.7265625" customWidth="1"/>
+    <col min="4" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>454</v>
       </c>
@@ -13427,1763 +13477,2467 @@
         <v>501</v>
       </c>
       <c r="C1" s="26" t="s">
+        <v>520</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="E1" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2" t="str">
-        <f>VLOOKUP(A2,H:I,2,0)</f>
+        <f t="shared" ref="B2:C33" si="0">VLOOKUP(A2,J:K,2,0)</f>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D2" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G2" s="3">
         <v>15255000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="str">
-        <f>VLOOKUP(A3,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D3" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G3" s="3">
         <v>720000</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" t="str">
-        <f>VLOOKUP(A4,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D4" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G4" s="3">
         <v>1900000</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="B5" t="str">
-        <f>VLOOKUP(A5,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D5" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G5" s="3">
         <v>150000</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="J5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="K5" s="27" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L5" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="M5" s="31"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="str">
-        <f>VLOOKUP(A6,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D6" s="29">
+        <v>10150008</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G6" s="3">
         <v>370000</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="J6" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="I6" s="27" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K6" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="L6" s="31" t="s">
+        <v>516</v>
+      </c>
+      <c r="M6" s="31"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7" t="str">
-        <f>VLOOKUP(A7,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D7" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G7" s="3">
         <v>700000</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="J7" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="I7" s="27" t="s">
+      <c r="K7" s="27" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L7" s="32" t="s">
+        <v>491</v>
+      </c>
+      <c r="M7" s="31"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="str">
-        <f>VLOOKUP(A8,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D8" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G8" s="3">
         <v>60000</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="J8" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="K8" s="27" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L8" s="32" t="s">
+        <v>492</v>
+      </c>
+      <c r="M8" s="31"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="str">
-        <f>VLOOKUP(A9,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D9" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G9" s="3">
         <v>80000</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="J9" s="27" t="s">
         <v>302</v>
       </c>
-      <c r="I9" s="27" t="s">
+      <c r="K9" s="27" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L9" s="31" t="s">
+        <v>510</v>
+      </c>
+      <c r="M9" s="31"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="str">
-        <f>VLOOKUP(A10,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D10" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G10" s="3">
         <v>175000</v>
       </c>
-      <c r="H10" s="27" t="s">
-        <v>503</v>
-      </c>
-      <c r="I10" s="27" t="s">
+      <c r="J10" s="27" t="s">
+        <v>502</v>
+      </c>
+      <c r="K10" s="27" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L10" s="31" t="s">
+        <v>509</v>
+      </c>
+      <c r="M10" s="31"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="str">
-        <f>VLOOKUP(A11,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D11" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G11" s="3">
         <v>116000</v>
       </c>
-      <c r="H11" s="27" t="s">
+      <c r="J11" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="I11" s="27" t="s">
+      <c r="K11" s="27" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L11" s="31" t="s">
+        <v>519</v>
+      </c>
+      <c r="M11" s="31"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="str">
-        <f>VLOOKUP(A12,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D12" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G12" s="3">
         <v>380000</v>
       </c>
-      <c r="H12" s="27" t="s">
+      <c r="J12" s="27" t="s">
         <v>318</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="K12" s="27" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L12" s="31" t="s">
+        <v>513</v>
+      </c>
+      <c r="M12" s="31"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="str">
-        <f>VLOOKUP(A13,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D13" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G13" s="3">
         <v>238000</v>
       </c>
-      <c r="H13" s="27" t="s">
-        <v>504</v>
-      </c>
-      <c r="I13" s="27" t="s">
+      <c r="J13" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="K13" s="27" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L13" s="31" t="s">
+        <v>511</v>
+      </c>
+      <c r="M13" s="31"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <f>VLOOKUP(A14,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D14" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G14" s="3">
         <v>380000</v>
       </c>
-      <c r="H14" s="27" t="s">
+      <c r="J14" s="27" t="s">
         <v>326</v>
       </c>
-      <c r="I14" s="27" t="s">
+      <c r="K14" s="27" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L14" s="31" t="s">
+        <v>512</v>
+      </c>
+      <c r="M14" s="31"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="str">
-        <f>VLOOKUP(A15,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D15" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G15" s="3">
         <v>781410.04</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="J15" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="I15" s="27" t="s">
+      <c r="K15" s="27" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="L15" s="31" t="s">
+        <v>514</v>
+      </c>
+      <c r="M15" s="31"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <f>VLOOKUP(A16,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D16" s="29">
+        <v>10130007</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G16" s="3">
         <v>546345</v>
       </c>
-      <c r="H16" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="I16" s="27" t="s">
+      <c r="J16" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="K16" s="27" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="L16" s="31" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
       <c r="B17" t="str">
-        <f>VLOOKUP(A17,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D17" s="29">
+        <v>10130007</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G17" s="3">
         <v>546345</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
       <c r="B18" t="str">
-        <f>VLOOKUP(A18,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D18" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G18" s="3">
         <v>63333.34</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
       <c r="B19" t="str">
-        <f>VLOOKUP(A19,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D19" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G19" s="3">
         <v>123378.34</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>13</v>
       </c>
       <c r="B20" t="str">
-        <f>VLOOKUP(A20,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D20" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G20" s="3">
         <v>121797.11</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>13</v>
       </c>
       <c r="B21" t="str">
-        <f>VLOOKUP(A21,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D21" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G21" s="3">
         <v>6666.7</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
       <c r="B22" t="str">
-        <f>VLOOKUP(A22,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D22" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G22" s="3">
         <v>6666.7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="str">
-        <f>VLOOKUP(A23,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D23" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G23" s="3">
         <v>22611.27</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24" t="str">
-        <f>VLOOKUP(A24,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D24" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G24" s="3">
         <v>88278.13</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
       <c r="B25" t="str">
-        <f>VLOOKUP(A25,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D25" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G25" s="3">
         <v>26052.86</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
       <c r="B26" t="str">
-        <f>VLOOKUP(A26,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D26" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G26" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
       <c r="B27" t="str">
-        <f>VLOOKUP(A27,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D27" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G27" s="3">
         <v>1256.9000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>13</v>
       </c>
       <c r="B28" t="str">
-        <f>VLOOKUP(A28,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D28" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G28" s="3">
         <v>8700</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>13</v>
       </c>
       <c r="B29" t="str">
-        <f>VLOOKUP(A29,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C29" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E29" s="3">
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D29" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G29" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>13</v>
       </c>
       <c r="B30" t="str">
-        <f>VLOOKUP(A30,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C30" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D30" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G30" s="3">
         <v>4893801.5999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
       <c r="B31" t="str">
-        <f>VLOOKUP(A31,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E31" s="3">
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D31" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G31" s="3">
         <v>5360125.5999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>13</v>
       </c>
       <c r="B32" t="str">
-        <f>VLOOKUP(A32,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D32" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G32" s="3">
         <v>4585488.4000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="str">
-        <f>VLOOKUP(A33,H:I,2,0)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> CIDB Holdings Sdn Bhd</v>
       </c>
-      <c r="C33" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> CIDBH</v>
+      </c>
+      <c r="D33" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G33" s="3">
         <v>781410.04</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>162</v>
       </c>
       <c r="B34" t="str">
-        <f>VLOOKUP(A34,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D34" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="E34" s="3">
+        <f t="shared" ref="B34:C65" si="1">VLOOKUP(A34,J:K,2,0)</f>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D34" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="G34" s="3">
         <v>5695</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>162</v>
       </c>
       <c r="B35" t="str">
-        <f>VLOOKUP(A35,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C35" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E35" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D35" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G35" s="3">
         <v>1600000</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>162</v>
       </c>
       <c r="B36" t="str">
-        <f>VLOOKUP(A36,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E36" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D36" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G36" s="3">
         <v>467000</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>162</v>
       </c>
       <c r="B37" t="str">
-        <f>VLOOKUP(A37,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C37" t="s">
-        <v>161</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E37" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D37" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G37" s="3">
         <v>61250</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>162</v>
       </c>
       <c r="B38" t="str">
-        <f>VLOOKUP(A38,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C38" t="s">
-        <v>161</v>
-      </c>
-      <c r="D38" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E38" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D38" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G38" s="3">
         <v>61250</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>162</v>
       </c>
       <c r="B39" t="str">
-        <f>VLOOKUP(A39,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E39" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D39" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G39" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>162</v>
       </c>
       <c r="B40" t="str">
-        <f>VLOOKUP(A40,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C40" t="s">
-        <v>190</v>
-      </c>
-      <c r="D40" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E40" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D40" s="29">
+        <v>10120002</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G40" s="3">
         <v>1639627.33</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>162</v>
       </c>
       <c r="B41" t="str">
-        <f>VLOOKUP(A41,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C41" t="s">
-        <v>161</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E41" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D41" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G41" s="3">
         <v>77644.83</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>162</v>
       </c>
       <c r="B42" t="str">
-        <f>VLOOKUP(A42,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C42" t="s">
-        <v>199</v>
-      </c>
-      <c r="D42" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E42" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D42" s="29">
+        <v>10140008</v>
+      </c>
+      <c r="E42" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G42" s="3">
         <v>16848</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>162</v>
       </c>
       <c r="B43" t="str">
-        <f>VLOOKUP(A43,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C43" t="s">
-        <v>199</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E43" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D43" s="29">
+        <v>10140008</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G43" s="3">
         <v>16848</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>162</v>
       </c>
       <c r="B44" t="str">
-        <f>VLOOKUP(A44,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C44" t="s">
-        <v>161</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E44" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D44" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E44" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G44" s="3">
         <v>77644.83</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>162</v>
       </c>
       <c r="B45" t="str">
-        <f>VLOOKUP(A45,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C45" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E45" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D45" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E45" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G45" s="3">
         <v>280000</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>162</v>
       </c>
       <c r="B46" t="str">
-        <f>VLOOKUP(A46,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C46" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E46" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D46" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G46" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>162</v>
       </c>
       <c r="B47" t="str">
-        <f>VLOOKUP(A47,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C47" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E47" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D47" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E47" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G47" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>162</v>
       </c>
       <c r="B48" t="str">
-        <f>VLOOKUP(A48,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E48" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D48" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G48" s="3">
         <v>128245.7</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>162</v>
       </c>
       <c r="B49" t="str">
-        <f>VLOOKUP(A49,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C49" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E49" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D49" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G49" s="3">
         <v>19577.599999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>162</v>
       </c>
       <c r="B50" t="str">
-        <f>VLOOKUP(A50,H:I,2,0)</f>
-        <v xml:space="preserve"> CIDB E-Construct Services Sdn Bhd</v>
-      </c>
-      <c r="C50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E50" s="3">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDB Digital Sdn Bhd</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CIDBeC</v>
+      </c>
+      <c r="D50" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G50" s="3">
         <v>19577.599999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>241</v>
       </c>
       <c r="B51" t="str">
-        <f>VLOOKUP(A51,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C51" t="s">
-        <v>199</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E51" s="3">
+      <c r="C51" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D51" s="29">
+        <v>10140008</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>483</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G51" s="3">
         <v>108000</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>241</v>
       </c>
       <c r="B52" t="str">
-        <f>VLOOKUP(A52,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C52" t="s">
-        <v>12</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="C52" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D52" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G52" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>241</v>
       </c>
       <c r="B53" t="str">
-        <f>VLOOKUP(A53,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C53" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E53" s="3">
+      <c r="C53" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D53" s="30">
+        <v>10130007</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G53" s="3">
         <v>245200</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>241</v>
       </c>
       <c r="B54" t="str">
-        <f>VLOOKUP(A54,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C54" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="C54" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D54" s="30">
+        <v>10130007</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G54" s="3">
         <v>151300</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>241</v>
       </c>
       <c r="B55" t="str">
-        <f>VLOOKUP(A55,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C55" t="s">
-        <v>161</v>
-      </c>
-      <c r="D55" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E55" s="3">
+      <c r="C55" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D55" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E55" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G55" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>241</v>
       </c>
       <c r="B56" t="str">
-        <f>VLOOKUP(A56,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C56" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D56" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E56" s="3">
+      <c r="C56" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D56" s="30">
+        <v>10130007</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G56" s="3">
         <v>245200</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>241</v>
       </c>
       <c r="B57" t="str">
-        <f>VLOOKUP(A57,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C57" t="s">
-        <v>78</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="C57" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D57" s="29">
+        <v>10130007</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G57" s="3">
         <v>151300</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>241</v>
       </c>
       <c r="B58" t="str">
-        <f>VLOOKUP(A58,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C58" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="C58" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D58" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E58" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F58" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G58" s="3">
         <v>25336.799999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>241</v>
       </c>
       <c r="B59" t="str">
-        <f>VLOOKUP(A59,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="C59" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D59" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E59" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F59" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G59" s="3">
         <v>25158.6</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>241</v>
       </c>
       <c r="B60" t="str">
-        <f>VLOOKUP(A60,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CREAM</v>
       </c>
-      <c r="C60" t="s">
-        <v>161</v>
-      </c>
-      <c r="D60" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="C60" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CREAM</v>
+      </c>
+      <c r="D60" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E60" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G60" s="3">
         <v>8432.11</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>286</v>
       </c>
       <c r="B61" t="str">
-        <f>VLOOKUP(A61,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CLAB</v>
       </c>
-      <c r="C61" t="s">
-        <v>12</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E61" s="3">
+      <c r="C61" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CLAB</v>
+      </c>
+      <c r="D61" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F61" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G61" s="3">
         <v>1500000</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>286</v>
       </c>
       <c r="B62" t="str">
-        <f>VLOOKUP(A62,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CLAB</v>
       </c>
-      <c r="C62" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="C62" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CLAB</v>
+      </c>
+      <c r="D62" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E62" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F62" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G62" s="3">
         <v>353970.88</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>286</v>
       </c>
       <c r="B63" t="str">
-        <f>VLOOKUP(A63,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CLAB</v>
       </c>
-      <c r="C63" t="s">
-        <v>12</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E63" s="3">
+      <c r="C63" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CLAB</v>
+      </c>
+      <c r="D63" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E63" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G63" s="3">
         <v>306244.8</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>286</v>
       </c>
       <c r="B64" t="str">
-        <f>VLOOKUP(A64,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> CLAB</v>
       </c>
-      <c r="C64" t="s">
-        <v>12</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E64" s="3">
+      <c r="C64" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> CLAB</v>
+      </c>
+      <c r="D64" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E64" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G64" s="3">
         <v>161212.42000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>302</v>
       </c>
       <c r="B65" t="str">
-        <f>VLOOKUP(A65,H:I,2,0)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> ABM Selangor Sdn Bhd</v>
       </c>
-      <c r="C65" t="s">
-        <v>12</v>
-      </c>
-      <c r="D65" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E65" s="3">
+      <c r="C65" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve"> ABMSbh</v>
+      </c>
+      <c r="D65" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E65" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G65" s="3">
         <v>91440</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>302</v>
       </c>
       <c r="B66" t="str">
-        <f>VLOOKUP(A66,H:I,2,0)</f>
+        <f t="shared" ref="B66:C97" si="2">VLOOKUP(A66,J:K,2,0)</f>
         <v xml:space="preserve"> ABM Selangor Sdn Bhd</v>
       </c>
-      <c r="C66" t="s">
-        <v>12</v>
-      </c>
-      <c r="D66" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="C66" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMSbh</v>
+      </c>
+      <c r="D66" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E66" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F66" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G66" s="3">
         <v>70104</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>313</v>
       </c>
       <c r="B67" t="str">
-        <f>VLOOKUP(A67,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Utara Sdn Bhd</v>
       </c>
-      <c r="C67" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E67" s="3">
+      <c r="C67" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMU</v>
+      </c>
+      <c r="D67" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E67" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F67" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G67" s="3">
         <v>91440</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>318</v>
       </c>
       <c r="B68" t="str">
-        <f>VLOOKUP(A68,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Terengganu Sdn Bhd</v>
       </c>
-      <c r="C68" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E68" s="3">
+      <c r="C68" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMT</v>
+      </c>
+      <c r="D68" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E68" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F68" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G68" s="3">
         <v>91440</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>318</v>
       </c>
       <c r="B69" t="str">
-        <f>VLOOKUP(A69,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Terengganu Sdn Bhd</v>
       </c>
-      <c r="C69" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E69" s="3">
+      <c r="C69" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMT</v>
+      </c>
+      <c r="D69" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E69" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F69" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G69" s="3">
         <v>5388</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>326</v>
       </c>
       <c r="B70" t="str">
-        <f>VLOOKUP(A70,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Sarawak Sdn Bhd</v>
       </c>
-      <c r="C70" t="s">
-        <v>12</v>
-      </c>
-      <c r="D70" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E70" s="3">
+      <c r="C70" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMSrwk</v>
+      </c>
+      <c r="D70" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E70" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F70" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G70" s="3">
         <v>76200</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>326</v>
       </c>
       <c r="B71" t="str">
-        <f>VLOOKUP(A71,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Sarawak Sdn Bhd</v>
       </c>
-      <c r="C71" t="s">
-        <v>19</v>
-      </c>
-      <c r="D71" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E71" s="3">
+      <c r="C71" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMSrwk</v>
+      </c>
+      <c r="D71" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E71" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F71" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G71" s="3">
         <v>48640</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>326</v>
       </c>
       <c r="B72" t="str">
-        <f>VLOOKUP(A72,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Sarawak Sdn Bhd</v>
       </c>
-      <c r="C72" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="C72" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMSrwk</v>
+      </c>
+      <c r="D72" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E72" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F72" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G72" s="3">
         <v>2032</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>326</v>
       </c>
       <c r="B73" t="str">
-        <f>VLOOKUP(A73,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Sarawak Sdn Bhd</v>
       </c>
-      <c r="C73" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E73" s="3">
+      <c r="C73" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMSrwk</v>
+      </c>
+      <c r="D73" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E73" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G73" s="3">
         <v>2032</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>326</v>
       </c>
       <c r="B74" t="str">
-        <f>VLOOKUP(A74,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> ABM Sarawak Sdn Bhd</v>
       </c>
-      <c r="C74" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E74" s="3">
+      <c r="C74" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> ABMSrwk</v>
+      </c>
+      <c r="D74" s="29">
+        <v>10170003</v>
+      </c>
+      <c r="E74" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="F74" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G74" s="3">
         <v>48640</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>349</v>
       </c>
       <c r="B75" t="str">
-        <f>VLOOKUP(A75,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C75" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E75" s="3">
+      <c r="C75" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D75" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E75" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F75" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G75" s="3">
         <v>465000</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>349</v>
       </c>
       <c r="B76" t="str">
-        <f>VLOOKUP(A76,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C76" t="s">
-        <v>161</v>
-      </c>
-      <c r="D76" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="C76" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D76" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F76" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G76" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>349</v>
       </c>
       <c r="B77" t="str">
-        <f>VLOOKUP(A77,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C77" t="s">
-        <v>161</v>
-      </c>
-      <c r="D77" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E77" s="3">
+      <c r="C77" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D77" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E77" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F77" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G77" s="3">
         <v>200000</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>349</v>
       </c>
       <c r="B78" t="str">
-        <f>VLOOKUP(A78,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C78" t="s">
-        <v>27</v>
-      </c>
-      <c r="D78" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E78" s="3">
+      <c r="C78" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D78" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E78" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F78" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G78" s="3">
         <v>385000</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>349</v>
       </c>
       <c r="B79" t="str">
-        <f>VLOOKUP(A79,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C79" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E79" s="3">
+      <c r="C79" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D79" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F79" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G79" s="3">
         <v>395000</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>349</v>
       </c>
       <c r="B80" t="str">
-        <f>VLOOKUP(A80,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C80" t="s">
-        <v>27</v>
-      </c>
-      <c r="D80" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E80" s="3">
+      <c r="C80" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D80" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E80" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F80" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G80" s="3">
         <v>169000</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>349</v>
       </c>
       <c r="B81" t="str">
-        <f>VLOOKUP(A81,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C81" t="s">
-        <v>27</v>
-      </c>
-      <c r="D81" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="C81" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D81" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E81" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F81" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G81" s="3">
         <v>250000</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>349</v>
       </c>
       <c r="B82" t="str">
-        <f>VLOOKUP(A82,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C82" t="s">
-        <v>27</v>
-      </c>
-      <c r="D82" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E82" s="3">
+      <c r="C82" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D82" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E82" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F82" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="G82" s="3">
         <v>145500</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>349</v>
       </c>
       <c r="B83" t="str">
-        <f>VLOOKUP(A83,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C83" t="s">
-        <v>12</v>
-      </c>
-      <c r="D83" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="C83" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D83" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E83" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F83" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G83" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>349</v>
       </c>
       <c r="B84" t="str">
-        <f>VLOOKUP(A84,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C84" t="s">
-        <v>12</v>
-      </c>
-      <c r="D84" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E84" s="3">
+      <c r="C84" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D84" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E84" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F84" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G84" s="3">
         <v>77100</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>349</v>
       </c>
       <c r="B85" t="str">
-        <f>VLOOKUP(A85,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C85" t="s">
-        <v>12</v>
-      </c>
-      <c r="D85" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E85" s="3">
+      <c r="C85" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D85" s="29">
+        <v>10150009</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="F85" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G85" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>349</v>
       </c>
       <c r="B86" t="str">
-        <f>VLOOKUP(A86,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C86" t="s">
-        <v>161</v>
-      </c>
-      <c r="D86" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E86" s="3">
+      <c r="C86" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D86" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E86" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F86" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G86" s="3">
         <v>97258.66</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>349</v>
       </c>
       <c r="B87" t="str">
-        <f>VLOOKUP(A87,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C87" t="s">
-        <v>161</v>
-      </c>
-      <c r="D87" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E87" s="3">
+      <c r="C87" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D87" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F87" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G87" s="3">
         <v>34699.68</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>349</v>
       </c>
       <c r="B88" t="str">
-        <f>VLOOKUP(A88,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C88" t="s">
-        <v>161</v>
-      </c>
-      <c r="D88" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E88" s="3">
+      <c r="C88" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D88" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F88" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G88" s="3">
         <v>65950.080000000002</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>349</v>
       </c>
       <c r="B89" t="str">
-        <f>VLOOKUP(A89,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C89" t="s">
-        <v>161</v>
-      </c>
-      <c r="D89" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="C89" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D89" s="29">
+        <v>10140007</v>
+      </c>
+      <c r="E89" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G89" s="3">
         <v>148113.60000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>349</v>
       </c>
       <c r="B90" t="str">
-        <f>VLOOKUP(A90,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C90" t="s">
-        <v>27</v>
-      </c>
-      <c r="D90" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E90" s="3">
+      <c r="C90" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D90" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E90" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F90" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G90" s="3">
         <v>13748.4</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>349</v>
       </c>
       <c r="B91" t="str">
-        <f>VLOOKUP(A91,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C91" t="s">
-        <v>27</v>
-      </c>
-      <c r="D91" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="C91" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D91" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E91" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F91" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G91" s="3">
         <v>20103.439999999999</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>349</v>
       </c>
       <c r="B92" t="str">
-        <f>VLOOKUP(A92,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C92" t="s">
-        <v>27</v>
-      </c>
-      <c r="D92" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E92" s="3">
+      <c r="C92" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D92" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E92" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F92" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G92" s="3">
         <v>106776.61</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>349</v>
       </c>
       <c r="B93" t="str">
-        <f>VLOOKUP(A93,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C93" t="s">
-        <v>27</v>
-      </c>
-      <c r="D93" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E93" s="3">
+      <c r="C93" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D93" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E93" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F93" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G93" s="3">
         <v>8899.2000000000007</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>349</v>
       </c>
       <c r="B94" t="str">
-        <f>VLOOKUP(A94,H:I,2,0)</f>
+        <f t="shared" si="2"/>
         <v xml:space="preserve"> CIDB IBS Sdn Bhd</v>
       </c>
-      <c r="C94" t="s">
-        <v>27</v>
-      </c>
-      <c r="D94" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="C94" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> CIDB IBS</v>
+      </c>
+      <c r="D94" s="29">
+        <v>10170004</v>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="F94" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="G94" s="3">
         <v>101900</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E94" xr:uid="{357F5962-F6D2-46FD-BFC8-B16168739F3B}"/>
+  <autoFilter ref="A1:G94" xr:uid="{357F5962-F6D2-46FD-BFC8-B16168739F3B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>